--- a/main/7_28kHz_Data/all_sessions_labels.xlsx
+++ b/main/7_28kHz_Data/all_sessions_labels.xlsx
@@ -464,17 +464,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -6515,17 +6515,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -11891,17 +11891,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -16992,17 +16992,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -22238,12 +22238,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ROIs</t>
+          <t>Cells</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Timepoints</t>
+          <t>Frames</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -22557,7 +22557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -22576,7 +22576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -22629,17 +22629,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -28430,17 +28430,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -34656,17 +34656,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -40932,17 +40932,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -46033,17 +46033,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -51859,17 +51859,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -57160,17 +57160,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
@@ -62836,17 +62836,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Trial_Type</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Action_choice</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Reward</t>
         </is>
       </c>
     </row>
